--- a/BOM/TDS_Meter/eSpark_BOM_TDS_Meter.xlsx
+++ b/BOM/TDS_Meter/eSpark_BOM_TDS_Meter.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\TDS_Meter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA7F435-6E7F-4361-A985-3BCCA1D6E4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D635BE-3CE8-4DFC-BC17-1679EDC892BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
   <si>
     <t>Component list</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>HDK</t>
-  </si>
-  <si>
-    <t>Comment</t>
   </si>
   <si>
     <t>0.1uF</t>
@@ -274,6 +271,9 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
 </sst>
 </file>
@@ -297,6 +297,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -310,6 +311,7 @@
       <sz val="12"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -903,6 +905,33 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -925,27 +954,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -955,12 +963,6 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1308,16 +1310,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="18" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -1338,15 +1340,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="60"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="69"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1357,7 +1359,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1382,7 +1384,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1396,7 +1398,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="61"/>
+      <c r="S3" s="70"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1407,7 +1409,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1421,7 +1423,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="62"/>
+      <c r="S4" s="71"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1446,7 +1448,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="62"/>
+      <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1467,7 +1469,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="62"/>
+      <c r="S6" s="71"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1488,7 +1490,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="62"/>
+      <c r="S7" s="71"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1509,7 +1511,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="62"/>
+      <c r="S8" s="71"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1517,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>6</v>
@@ -1535,37 +1537,37 @@
         <v>37</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="K9" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="R9" s="32" t="s">
+      <c r="S9" s="32" t="s">
         <v>59</v>
-      </c>
-      <c r="S9" s="32" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1574,8 +1576,8 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="67" t="s">
-        <v>62</v>
+      <c r="C10" s="59" t="s">
+        <v>61</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>7</v>
@@ -1593,13 +1595,13 @@
         <v>38</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L10" s="47">
         <v>1</v>
@@ -1611,8 +1613,8 @@
       <c r="N10" s="46">
         <v>100</v>
       </c>
-      <c r="O10" s="73" t="s">
-        <v>70</v>
+      <c r="O10" s="65" t="s">
+        <v>69</v>
       </c>
       <c r="P10" s="53">
         <v>3.3999999999999998E-3</v>
@@ -1630,8 +1632,8 @@
         <f t="shared" ref="B11:B17" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="68" t="s">
-        <v>45</v>
+      <c r="C11" s="60" t="s">
+        <v>44</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>8</v>
@@ -1643,19 +1645,19 @@
         <v>26</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L11" s="51">
         <v>2</v>
@@ -1665,16 +1667,16 @@
         <v>10</v>
       </c>
       <c r="N11" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O11" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="50"/>
@@ -1685,8 +1687,8 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="67" t="s">
-        <v>63</v>
+      <c r="C12" s="59" t="s">
+        <v>62</v>
       </c>
       <c r="D12" s="46" t="s">
         <v>9</v>
@@ -1697,20 +1699,20 @@
       <c r="F12" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="69">
+      <c r="G12" s="61">
         <v>61300611121</v>
       </c>
       <c r="H12" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="70" t="s">
+      <c r="I12" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="46" t="s">
-        <v>69</v>
-      </c>
       <c r="K12" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L12" s="47">
         <v>1</v>
@@ -1722,14 +1724,14 @@
       <c r="N12" s="46">
         <v>50</v>
       </c>
-      <c r="O12" s="71" t="s">
-        <v>70</v>
+      <c r="O12" s="63" t="s">
+        <v>69</v>
       </c>
       <c r="P12" s="53">
         <v>1.2E-2</v>
       </c>
       <c r="Q12" s="53">
-        <f t="shared" ref="Q11:Q17" si="2">P12*N12</f>
+        <f t="shared" ref="Q12:Q17" si="2">P12*N12</f>
         <v>0.6</v>
       </c>
       <c r="R12" s="48"/>
@@ -1741,8 +1743,8 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="68" t="s">
-        <v>64</v>
+      <c r="C13" s="60" t="s">
+        <v>63</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>10</v>
@@ -1760,13 +1762,13 @@
         <v>40</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -1778,8 +1780,8 @@
       <c r="N13" s="50">
         <v>10</v>
       </c>
-      <c r="O13" s="72" t="s">
-        <v>70</v>
+      <c r="O13" s="64" t="s">
+        <v>69</v>
       </c>
       <c r="P13" s="54">
         <v>0.1212</v>
@@ -1797,8 +1799,8 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="67" t="s">
-        <v>65</v>
+      <c r="C14" s="59" t="s">
+        <v>64</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>11</v>
@@ -1816,13 +1818,13 @@
         <v>38</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="47">
         <v>1</v>
@@ -1834,8 +1836,8 @@
       <c r="N14" s="46">
         <v>100</v>
       </c>
-      <c r="O14" s="71" t="s">
-        <v>70</v>
+      <c r="O14" s="63" t="s">
+        <v>69</v>
       </c>
       <c r="P14" s="53">
         <v>1.4E-3</v>
@@ -1853,8 +1855,8 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="68" t="s">
-        <v>65</v>
+      <c r="C15" s="60" t="s">
+        <v>64</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>12</v>
@@ -1863,7 +1865,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>30</v>
@@ -1872,13 +1874,13 @@
         <v>41</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -1890,8 +1892,8 @@
       <c r="N15" s="50">
         <v>10</v>
       </c>
-      <c r="O15" s="72" t="s">
-        <v>70</v>
+      <c r="O15" s="64" t="s">
+        <v>69</v>
       </c>
       <c r="P15" s="54">
         <v>6.9599999999999995E-2</v>
@@ -1909,8 +1911,8 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>65</v>
+      <c r="C16" s="59" t="s">
+        <v>64</v>
       </c>
       <c r="D16" s="46" t="s">
         <v>13</v>
@@ -1927,12 +1929,14 @@
       <c r="H16" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="46"/>
+      <c r="I16" s="46" t="s">
+        <v>60</v>
+      </c>
       <c r="J16" s="46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K16" s="46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L16" s="47">
         <v>2</v>
@@ -1944,8 +1948,8 @@
       <c r="N16" s="46">
         <v>100</v>
       </c>
-      <c r="O16" s="71" t="s">
-        <v>70</v>
+      <c r="O16" s="63" t="s">
+        <v>69</v>
       </c>
       <c r="P16" s="53">
         <v>1.1999999999999999E-3</v>
@@ -1963,8 +1967,8 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="68" t="s">
-        <v>65</v>
+      <c r="C17" s="60" t="s">
+        <v>64</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>14</v>
@@ -1973,7 +1977,7 @@
         <v>23</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" s="50" t="s">
         <v>31</v>
@@ -1982,13 +1986,13 @@
         <v>42</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -2000,8 +2004,8 @@
       <c r="N17" s="50">
         <v>10</v>
       </c>
-      <c r="O17" s="72" t="s">
-        <v>70</v>
+      <c r="O17" s="64" t="s">
+        <v>69</v>
       </c>
       <c r="P17" s="54">
         <v>7.4999999999999997E-2</v>
@@ -2027,17 +2031,17 @@
       <c r="K18" s="37"/>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
-      <c r="N18" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="76">
+      <c r="N18" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="O18" s="77"/>
+      <c r="P18" s="77"/>
+      <c r="Q18" s="66">
         <f>SUM(Q10:Q17)</f>
         <v>3.8580000000000005</v>
       </c>
-      <c r="R18" s="63"/>
-      <c r="S18" s="64"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="73"/>
     </row>
     <row r="19" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -2053,17 +2057,17 @@
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="O19" s="75"/>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="77">
+      <c r="N19" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="67">
         <f>Q18/5</f>
         <v>0.77160000000000006</v>
       </c>
-      <c r="R19" s="65"/>
-      <c r="S19" s="66"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/BOM/TDS_Meter/eSpark_BOM_TDS_Meter.xlsx
+++ b/BOM/TDS_Meter/eSpark_BOM_TDS_Meter.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\TDS_Meter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\OliverStanton-WaterMonitor\BOM\TDS_Meter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D635BE-3CE8-4DFC-BC17-1679EDC892BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -279,7 +278,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -747,7 +746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -963,6 +962,15 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1304,7 +1312,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1635,51 +1643,51 @@
       <c r="C11" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="51" t="s">
+      <c r="I11" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="50" t="s">
+      <c r="J11" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="50" t="s">
+      <c r="K11" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="51">
+      <c r="L11" s="79">
         <v>2</v>
       </c>
-      <c r="M11" s="50">
+      <c r="M11" s="78">
         <f t="shared" ref="M11:M17" si="1">L11*5</f>
         <v>10</v>
       </c>
-      <c r="N11" s="51" t="s">
+      <c r="N11" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="O11" s="50" t="s">
+      <c r="O11" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="P11" s="51" t="s">
+      <c r="P11" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="54" t="s">
+      <c r="Q11" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="51"/>
-      <c r="S11" s="50"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="78"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -2078,13 +2086,13 @@
     <mergeCell ref="N19:P19"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O12" r:id="rId1" xr:uid="{977987ED-9FE0-47B0-AE46-5E17A351811B}"/>
-    <hyperlink ref="O13" r:id="rId2" xr:uid="{906AFE4B-000D-4BD8-84A7-A8A2395DE921}"/>
-    <hyperlink ref="O10" r:id="rId3" xr:uid="{A56A9E6B-703A-4BF6-8798-9FD31E2A2303}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{5B97FE88-D43B-436B-AB56-8FA9D5EEE38F}"/>
-    <hyperlink ref="O15" r:id="rId5" xr:uid="{ACC32550-621C-44EA-AC13-21D551231C73}"/>
-    <hyperlink ref="O16" r:id="rId6" xr:uid="{7CD3887C-D4F2-4263-96AB-59D006D9F851}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{FE696CC9-9A60-4A3E-A77B-33D07A936CD4}"/>
+    <hyperlink ref="O12" r:id="rId1"/>
+    <hyperlink ref="O13" r:id="rId2"/>
+    <hyperlink ref="O10" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>

--- a/BOM/TDS_Meter/eSpark_BOM_TDS_Meter.xlsx
+++ b/BOM/TDS_Meter/eSpark_BOM_TDS_Meter.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -232,13 +232,6 @@
     <t>(TDS_Meter)</t>
   </si>
   <si>
-    <t xml:space="preserve">PZ254V-11-02P
-</t>
-  </si>
-  <si>
-    <t>C492401</t>
-  </si>
-  <si>
     <t>LCSC</t>
   </si>
   <si>
@@ -273,6 +266,12 @@
   </si>
   <si>
     <t>Value</t>
+  </si>
+  <si>
+    <t>PZ254V-11-06P</t>
+  </si>
+  <si>
+    <t>C492405</t>
   </si>
 </sst>
 </file>
@@ -746,7 +745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -913,9 +912,6 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,6 +926,15 @@
     </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -962,15 +967,6 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1348,15 +1344,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="69"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1406,7 +1402,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="70"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1431,7 +1427,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="71"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1456,7 +1452,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="71"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1477,7 +1473,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="71"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1498,7 +1494,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="71"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1519,7 +1515,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="71"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1551,7 +1547,7 @@
         <v>52</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L9" s="31" t="s">
         <v>49</v>
@@ -1606,7 +1602,7 @@
         <v>60</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K10" s="46" t="s">
         <v>43</v>
@@ -1621,8 +1617,8 @@
       <c r="N10" s="46">
         <v>100</v>
       </c>
-      <c r="O10" s="65" t="s">
-        <v>69</v>
+      <c r="O10" s="64" t="s">
+        <v>67</v>
       </c>
       <c r="P10" s="53">
         <v>3.3999999999999998E-3</v>
@@ -1643,51 +1639,51 @@
       <c r="C11" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="78" t="s">
+      <c r="F11" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="78" t="s">
+      <c r="H11" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="79" t="s">
+      <c r="I11" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="78" t="s">
+      <c r="J11" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="78" t="s">
+      <c r="K11" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="79">
+      <c r="L11" s="68">
         <v>2</v>
       </c>
-      <c r="M11" s="78">
+      <c r="M11" s="67">
         <f t="shared" ref="M11:M17" si="1">L11*5</f>
         <v>10</v>
       </c>
-      <c r="N11" s="79" t="s">
+      <c r="N11" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="O11" s="78" t="s">
+      <c r="O11" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="P11" s="79" t="s">
+      <c r="P11" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="80" t="s">
+      <c r="Q11" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="79"/>
-      <c r="S11" s="78"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="67"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1713,11 +1709,11 @@
       <c r="H12" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="62" t="s">
-        <v>67</v>
+      <c r="I12" s="46" t="s">
+        <v>79</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="K12" s="46" t="s">
         <v>60</v>
@@ -1730,17 +1726,17 @@
         <v>5</v>
       </c>
       <c r="N12" s="46">
-        <v>50</v>
-      </c>
-      <c r="O12" s="63" t="s">
-        <v>69</v>
+        <v>20</v>
+      </c>
+      <c r="O12" s="62" t="s">
+        <v>67</v>
       </c>
       <c r="P12" s="53">
-        <v>1.2E-2</v>
+        <v>3.4200000000000001E-2</v>
       </c>
       <c r="Q12" s="53">
         <f t="shared" ref="Q12:Q17" si="2">P12*N12</f>
-        <v>0.6</v>
+        <v>0.68400000000000005</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
@@ -1773,7 +1769,7 @@
         <v>60</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K13" s="50" t="s">
         <v>60</v>
@@ -1788,8 +1784,8 @@
       <c r="N13" s="50">
         <v>10</v>
       </c>
-      <c r="O13" s="64" t="s">
-        <v>69</v>
+      <c r="O13" s="63" t="s">
+        <v>67</v>
       </c>
       <c r="P13" s="54">
         <v>0.1212</v>
@@ -1829,7 +1825,7 @@
         <v>60</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K14" s="46" t="s">
         <v>45</v>
@@ -1844,8 +1840,8 @@
       <c r="N14" s="46">
         <v>100</v>
       </c>
-      <c r="O14" s="63" t="s">
-        <v>69</v>
+      <c r="O14" s="62" t="s">
+        <v>67</v>
       </c>
       <c r="P14" s="53">
         <v>1.4E-3</v>
@@ -1873,7 +1869,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>30</v>
@@ -1885,7 +1881,7 @@
         <v>60</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K15" s="50" t="s">
         <v>46</v>
@@ -1900,8 +1896,8 @@
       <c r="N15" s="50">
         <v>10</v>
       </c>
-      <c r="O15" s="64" t="s">
-        <v>69</v>
+      <c r="O15" s="63" t="s">
+        <v>67</v>
       </c>
       <c r="P15" s="54">
         <v>6.9599999999999995E-2</v>
@@ -1941,7 +1937,7 @@
         <v>60</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K16" s="46" t="s">
         <v>47</v>
@@ -1956,8 +1952,8 @@
       <c r="N16" s="46">
         <v>100</v>
       </c>
-      <c r="O16" s="63" t="s">
-        <v>69</v>
+      <c r="O16" s="62" t="s">
+        <v>67</v>
       </c>
       <c r="P16" s="53">
         <v>1.1999999999999999E-3</v>
@@ -1985,7 +1981,7 @@
         <v>23</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G17" s="50" t="s">
         <v>31</v>
@@ -1997,7 +1993,7 @@
         <v>60</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K17" s="50" t="s">
         <v>48</v>
@@ -2012,8 +2008,8 @@
       <c r="N17" s="50">
         <v>10</v>
       </c>
-      <c r="O17" s="64" t="s">
-        <v>69</v>
+      <c r="O17" s="63" t="s">
+        <v>67</v>
       </c>
       <c r="P17" s="54">
         <v>7.4999999999999997E-2</v>
@@ -2039,17 +2035,17 @@
       <c r="K18" s="37"/>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
-      <c r="N18" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="O18" s="77"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="66">
+      <c r="N18" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="65">
         <f>SUM(Q10:Q17)</f>
-        <v>3.8580000000000005</v>
-      </c>
-      <c r="R18" s="72"/>
-      <c r="S18" s="73"/>
+        <v>3.9420000000000002</v>
+      </c>
+      <c r="R18" s="74"/>
+      <c r="S18" s="75"/>
     </row>
     <row r="19" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -2065,17 +2061,17 @@
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="67">
+      <c r="N19" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="66">
         <f>Q18/5</f>
-        <v>0.77160000000000006</v>
-      </c>
-      <c r="R19" s="74"/>
-      <c r="S19" s="75"/>
+        <v>0.78839999999999999</v>
+      </c>
+      <c r="R19" s="76"/>
+      <c r="S19" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2086,13 +2082,13 @@
     <mergeCell ref="N19:P19"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O12" r:id="rId1"/>
-    <hyperlink ref="O13" r:id="rId2"/>
-    <hyperlink ref="O10" r:id="rId3"/>
-    <hyperlink ref="O14" r:id="rId4"/>
-    <hyperlink ref="O15" r:id="rId5"/>
-    <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O13" r:id="rId1"/>
+    <hyperlink ref="O10" r:id="rId2"/>
+    <hyperlink ref="O14" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O12" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
